--- a/attention/quant_lightning_indexer/docs/mxfp8_stc.xlsx
+++ b/attention/quant_lightning_indexer/docs/mxfp8_stc.xlsx
@@ -2379,10 +2379,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F20" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -2446,7 +2444,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>s1=8</t>
+          <t>s1=5奇数非2的幂</t>
         </is>
       </c>
     </row>
@@ -2476,21 +2474,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2543,7 +2539,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>s1=16</t>
+          <t>s1=7奇数</t>
         </is>
       </c>
     </row>
@@ -2573,10 +2569,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="F22" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -2640,7 +2634,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>s1=32较长query</t>
+          <t>s1=11奇数质数较长query</t>
         </is>
       </c>
     </row>
@@ -2772,10 +2766,8 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="G24" s="2" t="n">
+        <v>129</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2834,7 +2826,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>s2=256(2个基本块)</t>
+          <t>s2=129奇数刚过s2BaseSize边界</t>
         </is>
       </c>
     </row>
@@ -2869,10 +2861,8 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
+      <c r="G25" s="2" t="n">
+        <v>255</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2931,7 +2921,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>s2=512(4个基本块)</t>
+          <t>s2=255奇数(2^8-1)非对齐</t>
         </is>
       </c>
     </row>
@@ -2966,10 +2956,8 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
+      <c r="G26" s="2" t="n">
+        <v>333</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -3028,7 +3016,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>s2=1024(8个基本块)</t>
+          <t>s2=333奇数非2的幂</t>
         </is>
       </c>
     </row>
@@ -3160,10 +3148,8 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>4096</t>
-        </is>
+      <c r="G28" s="2" t="n">
+        <v>3001</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -3222,7 +3208,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>s2=4096+PA长序列</t>
+          <t>s2=3001奇数+PA长序列</t>
         </is>
       </c>
     </row>
@@ -3456,10 +3442,8 @@
           <t>256</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="H31" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -3513,7 +3497,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>g=2(mBaseSize=4)边界测试</t>
+          <t>g=3非2的幂(mBaseSize=6)质数边界测试</t>
         </is>
       </c>
     </row>
@@ -3553,10 +3537,8 @@
           <t>256</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="H32" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -3610,7 +3592,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>g=4(mBaseSize=8)边界测试</t>
+          <t>g=5非2的幂(mBaseSize=10)质数边界测试</t>
         </is>
       </c>
     </row>
@@ -3747,10 +3729,8 @@
           <t>256</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="H34" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -3804,7 +3784,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>g=16(mBaseSize=32)arch35支持值</t>
+          <t>g=12非2的幂(mBaseSize=24)合数</t>
         </is>
       </c>
     </row>
@@ -3941,10 +3921,8 @@
           <t>256</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="H36" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -3998,7 +3976,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>g=32(mBaseSize=64)arch35支持值</t>
+          <t>g=20非2的幂(mBaseSize=40)</t>
         </is>
       </c>
     </row>
@@ -7433,10 +7411,8 @@
           <t>8192</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="H72" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
@@ -7490,7 +7466,7 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>压力测试-全最大参数(b=32 s1=32 s2=8192 g=64 sparse=2048)</t>
+          <t>TND+PA非均匀4batch+causal+return_value+g=10非2的幂</t>
         </is>
       </c>
     </row>
@@ -7714,56 +7690,54 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F75" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -7781,7 +7755,7 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>压力测试-s1=1+maxG=64+causal+sparse=1</t>
+          <t>压力测试-s1=9奇数+maxG=64+causal+sparse=1</t>
         </is>
       </c>
     </row>
@@ -8403,41 +8377,39 @@
           <t>1024</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H82" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
           <t>512</t>
@@ -8460,7 +8432,7 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>组合测试-大G=64+PA+中等block</t>
+          <t>组合测试-g=36非2的幂+PA+中等block</t>
         </is>
       </c>
     </row>

--- a/attention/quant_lightning_indexer/docs/mxfp8_stc.xlsx
+++ b/attention/quant_lightning_indexer/docs/mxfp8_stc.xlsx
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>g=12非2的幂(mBaseSize=24)合数</t>
+          <t>g=13非2的幂(mBaseSize=26)奇数质数</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>g=20非2的幂(mBaseSize=40)</t>
+          <t>g=21非2的幂(mBaseSize=42)奇数合数(3×7)</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>组合测试-g=36非2的幂+PA+中等block</t>
+          <t>组合测试-g=33非2的幂奇数(3×11)+PA+中等block</t>
         </is>
       </c>
     </row>
